--- a/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/RelicConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97144BB-7141-40E2-9B5B-1B7399689FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E01AE4-ACAC-4BD7-8ADD-F690EFCCB7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4212" yWindow="4212" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RelicConfig" sheetId="1" r:id="rId1"/>
@@ -189,10 +189,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"multiplier":1.75}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BlockOnHpLossNextTurn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -253,6 +249,10 @@
   </si>
   <si>
     <t>HealOnCombatEnd</t>
+  </si>
+  <si>
+    <t>{"multiplier":0.25}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -877,13 +877,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>15</v>
@@ -900,7 +900,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -946,7 +946,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -955,7 +955,7 @@
         <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -969,16 +969,16 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>27</v>
@@ -992,16 +992,16 @@
         <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>29</v>
@@ -1015,13 +1015,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -1036,13 +1036,13 @@
         <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
@@ -1057,16 +1057,16 @@
         <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>35</v>
